--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -105,24 +105,6 @@
     <t>#精炼石</t>
   </si>
   <si>
-    <t>#魂环</t>
-  </si>
-  <si>
-    <t>#副本劵</t>
-  </si>
-  <si>
-    <t>#boss卷</t>
-  </si>
-  <si>
-    <t>#等级丹</t>
-  </si>
-  <si>
-    <t>#特戒</t>
-  </si>
-  <si>
-    <t>#特技</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -145,9 +127,6 @@
   </si>
   <si>
     <t>副本劵，等级丹，特戒自选</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1120,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1193,7 +1172,7 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
@@ -1238,30 +1217,14 @@
       <c r="P3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
@@ -1305,47 +1268,47 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:20">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1383,33 +1346,19 @@
         <v>70</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" ref="P6:P10" si="0">H6*900</f>
         <v>180000000</v>
       </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <f t="shared" ref="R6:R9" si="1">K6*90</f>
-        <v>6300</v>
-      </c>
-      <c r="S6" s="1">
-        <f t="shared" ref="S6:S9" si="2">N6*10</f>
-        <v>700</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:20">
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D17" si="3">E6+1</f>
+        <f t="shared" ref="D7:D19" si="1">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -1443,33 +1392,18 @@
         <v>80</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
       </c>
-      <c r="Q7" s="1">
-        <f t="shared" ref="Q7:Q11" si="4">H7*900</f>
-        <v>18000000</v>
-      </c>
-      <c r="R7" s="1">
-        <f t="shared" si="1"/>
-        <v>7200</v>
-      </c>
-      <c r="S7" s="1">
-        <f t="shared" si="2"/>
-        <v>800</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:20">
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2001</v>
       </c>
       <c r="E8" s="1">
@@ -1503,33 +1437,19 @@
         <v>90</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="0"/>
         <v>360000000</v>
       </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <f t="shared" si="1"/>
-        <v>8100</v>
-      </c>
-      <c r="S8" s="1">
-        <f t="shared" si="2"/>
-        <v>900</v>
-      </c>
-      <c r="T8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:20">
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3001</v>
       </c>
       <c r="E9" s="1">
@@ -1563,33 +1483,18 @@
         <v>100</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P9" s="1">
         <v>0</v>
       </c>
-      <c r="Q9" s="1">
-        <f t="shared" si="4"/>
-        <v>36000000</v>
-      </c>
-      <c r="R9" s="1">
-        <f t="shared" si="1"/>
-        <v>9000</v>
-      </c>
-      <c r="S9" s="1">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="T9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:21">
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4001</v>
       </c>
       <c r="E10" s="1">
@@ -1623,35 +1528,19 @@
         <v>1</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P10" s="1">
         <f t="shared" si="0"/>
         <v>540000000</v>
       </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="1">
-        <f t="shared" ref="T10:T17" si="5">K10*90</f>
-        <v>900</v>
-      </c>
-      <c r="U10" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:21">
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>5001</v>
       </c>
       <c r="E11" s="1">
@@ -1685,35 +1574,18 @@
         <v>1</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
       </c>
-      <c r="Q11" s="1">
-        <f t="shared" si="4"/>
-        <v>54000000</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="1">
-        <f t="shared" si="5"/>
-        <v>1800</v>
-      </c>
-      <c r="U11" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:21">
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>6001</v>
       </c>
       <c r="E12" s="1">
@@ -1747,35 +1619,19 @@
         <v>1</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P12" s="1">
         <f>H12*900</f>
         <v>720000000</v>
       </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1">
-        <f t="shared" si="5"/>
-        <v>2700</v>
-      </c>
-      <c r="U12" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:21">
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>7001</v>
       </c>
       <c r="E13" s="1">
@@ -1809,35 +1665,18 @@
         <v>1</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="P13" s="1">
         <v>0</v>
       </c>
-      <c r="Q13" s="1">
-        <f>H13*900</f>
-        <v>72000000</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1">
-        <f t="shared" si="5"/>
-        <v>3600</v>
-      </c>
-      <c r="U13" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:21">
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8001</v>
       </c>
       <c r="E14" s="1">
@@ -1871,35 +1710,19 @@
         <v>1</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P14" s="1">
         <f>H14*900</f>
         <v>900000000</v>
       </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
-      <c r="T14" s="1">
-        <f t="shared" si="5"/>
-        <v>4500</v>
-      </c>
-      <c r="U14" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:22">
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>9001</v>
       </c>
       <c r="E15" s="1">
@@ -1933,38 +1756,18 @@
         <v>1</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P15" s="1">
         <v>0</v>
       </c>
-      <c r="Q15" s="1">
-        <f>H15*900</f>
-        <v>90000000</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1">
-        <v>0</v>
-      </c>
-      <c r="T15" s="1">
-        <f t="shared" si="5"/>
-        <v>5400</v>
-      </c>
-      <c r="U15" s="1">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:20">
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>10001</v>
       </c>
       <c r="E16" s="1">
@@ -1998,29 +1801,15 @@
         <v>1</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1">
-        <f>H16*900*2</f>
-        <v>9000</v>
-      </c>
-      <c r="S16" s="1">
-        <v>0</v>
-      </c>
-      <c r="T16" s="1">
-        <f t="shared" si="5"/>
-        <v>6300</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:20">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>15001</v>
       </c>
       <c r="E17" s="1">
@@ -2054,32 +1843,92 @@
         <v>1</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1">
-        <f>H17*900*3</f>
-        <v>2700</v>
-      </c>
-      <c r="T17" s="1">
-        <f t="shared" si="5"/>
-        <v>6300</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="1"/>
+        <v>20001</v>
+      </c>
+      <c r="E18" s="1">
+        <v>21000</v>
+      </c>
+      <c r="F18" s="1">
+        <v>9</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4004</v>
+      </c>
+      <c r="H18" s="1">
+        <v>10</v>
+      </c>
+      <c r="I18" s="8">
+        <v>15</v>
+      </c>
+      <c r="J18" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K18" s="8">
+        <v>80</v>
+      </c>
+      <c r="L18" s="1">
+        <v>4</v>
+      </c>
+      <c r="M18" s="1">
+        <v>26</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="1"/>
+        <v>21001</v>
+      </c>
+      <c r="E19" s="1">
+        <v>25000</v>
+      </c>
+      <c r="F19" s="1">
+        <v>9</v>
+      </c>
+      <c r="G19" s="1">
+        <v>4004</v>
+      </c>
+      <c r="H19" s="1">
+        <v>10</v>
+      </c>
+      <c r="I19" s="8">
+        <v>15</v>
+      </c>
+      <c r="J19" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K19" s="8">
+        <v>80</v>
+      </c>
+      <c r="L19" s="1">
+        <v>4</v>
+      </c>
+      <c r="M19" s="1">
+        <v>22</v>
+      </c>
+      <c r="N19" s="1">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="9:11">
       <c r="I20" s="8"/>
@@ -2111,67 +1960,10 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="1">
-        <v>12</v>
-      </c>
-      <c r="D27" s="1">
-        <f>E16+1</f>
-        <v>15001</v>
-      </c>
-      <c r="E27" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F27" s="1">
-        <v>5</v>
-      </c>
-      <c r="G27" s="1">
-        <v>4004</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1</v>
-      </c>
-      <c r="I27" s="8">
-        <v>15</v>
-      </c>
-      <c r="J27" s="8">
-        <v>4014</v>
-      </c>
-      <c r="K27" s="8">
-        <v>80</v>
-      </c>
-      <c r="L27" s="1">
-        <v>4</v>
-      </c>
-      <c r="M27" s="1">
-        <v>22</v>
-      </c>
-      <c r="N27" s="1">
-        <v>1</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
-      <c r="S27" s="1">
-        <f>H27*900*3</f>
-        <v>2700</v>
-      </c>
-      <c r="T27" s="1">
-        <f>K27*90</f>
-        <v>7200</v>
-      </c>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="9:11">
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="9:11">
       <c r="I28" s="8"/>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -1861,7 +1861,7 @@
         <v>9</v>
       </c>
       <c r="G18" s="1">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="H18" s="1">
         <v>10</v>
@@ -1903,7 +1903,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="1">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="H19" s="1">
         <v>10</v>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -127,6 +127,18 @@
   </si>
   <si>
     <t>副本劵，等级丹，特戒自选</t>
+  </si>
+  <si>
+    <t>BOSS卷，等级丹，特戒自选</t>
+  </si>
+  <si>
+    <t>副本劵，等级丹，神技</t>
+  </si>
+  <si>
+    <t>BOSS劵，等级丹，魂骨自选</t>
+  </si>
+  <si>
+    <t>BOSS劵，等级丹，特戒自选</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1370,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D19" si="1">E6+1</f>
+        <f t="shared" ref="D7:D21" si="1">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -1843,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1885,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1930,15 +1942,89 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="1"/>
+        <v>25001</v>
+      </c>
+      <c r="E20" s="1">
+        <v>26000</v>
+      </c>
+      <c r="F20" s="1">
+        <v>9</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4004</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2</v>
+      </c>
+      <c r="I20" s="8">
+        <v>15</v>
+      </c>
+      <c r="J20" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K20" s="8">
+        <v>90</v>
+      </c>
+      <c r="L20" s="1">
+        <v>4</v>
+      </c>
+      <c r="M20" s="1">
+        <v>28</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="1"/>
+        <v>26001</v>
+      </c>
+      <c r="E21" s="1">
+        <v>30000</v>
+      </c>
+      <c r="F21" s="1">
+        <v>9</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4004</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2</v>
+      </c>
+      <c r="I21" s="8">
+        <v>15</v>
+      </c>
+      <c r="J21" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K21" s="8">
+        <v>90</v>
+      </c>
+      <c r="L21" s="1">
+        <v>4</v>
+      </c>
+      <c r="M21" s="1">
+        <v>22</v>
+      </c>
+      <c r="N21" s="1">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="9:11">
       <c r="I22" s="8"/>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -135,7 +135,7 @@
     <t>副本劵，等级丹，神技</t>
   </si>
   <si>
-    <t>BOSS劵，等级丹，魂骨自选</t>
+    <t>BOSS劵，等级丹，11技能自选</t>
   </si>
   <si>
     <t>BOSS劵，等级丹，特戒自选</t>
@@ -1975,7 +1975,7 @@
         <v>4</v>
       </c>
       <c r="M20" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N20" s="1">
         <v>1</v>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -1953,8 +1953,8 @@
       <c r="E20" s="1">
         <v>26000</v>
       </c>
-      <c r="F20" s="1">
-        <v>9</v>
+      <c r="F20" s="5">
+        <v>5</v>
       </c>
       <c r="G20" s="1">
         <v>4004</v>
@@ -1995,8 +1995,8 @@
       <c r="E21" s="1">
         <v>30000</v>
       </c>
-      <c r="F21" s="1">
-        <v>9</v>
+      <c r="F21" s="5">
+        <v>5</v>
       </c>
       <c r="G21" s="1">
         <v>4004</v>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -139,6 +139,12 @@
   </si>
   <si>
     <t>BOSS劵，等级丹，特戒自选</t>
+  </si>
+  <si>
+    <t>传世劵，等级丹，魂骨自选</t>
+  </si>
+  <si>
+    <t>传世劵，等级丹，特戒自选</t>
   </si>
 </sst>
 </file>
@@ -1370,7 +1376,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D21" si="1">E6+1</f>
+        <f t="shared" ref="D7:D23" si="1">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -2026,15 +2032,89 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="1"/>
+        <v>30001</v>
+      </c>
+      <c r="E22" s="1">
+        <v>31000</v>
+      </c>
+      <c r="F22" s="5">
+        <v>9</v>
+      </c>
+      <c r="G22" s="1">
+        <v>4004</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="8">
+        <v>15</v>
+      </c>
+      <c r="J22" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K22" s="8">
+        <v>90</v>
+      </c>
+      <c r="L22" s="1">
+        <v>4</v>
+      </c>
+      <c r="M22" s="1">
+        <v>28</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="1"/>
+        <v>31001</v>
+      </c>
+      <c r="E23" s="1">
+        <v>35000</v>
+      </c>
+      <c r="F23" s="5">
+        <v>9</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4004</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="8">
+        <v>15</v>
+      </c>
+      <c r="J23" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K23" s="8">
+        <v>90</v>
+      </c>
+      <c r="L23" s="1">
+        <v>4</v>
+      </c>
+      <c r="M23" s="1">
+        <v>22</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="9:11">
       <c r="I24" s="8"/>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -2047,7 +2047,7 @@
         <v>9</v>
       </c>
       <c r="G22" s="1">
-        <v>4004</v>
+        <v>4013</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         <v>9</v>
       </c>
       <c r="G23" s="1">
-        <v>4004</v>
+        <v>4013</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -102,9 +102,6 @@
     <t>#des</t>
   </si>
   <si>
-    <t>#精炼石</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -145,6 +142,9 @@
   </si>
   <si>
     <t>传世劵，等级丹，特戒自选</t>
+  </si>
+  <si>
+    <t>副本劵，等级丹，神器</t>
   </si>
 </sst>
 </file>
@@ -1232,9 +1232,7 @@
       <c r="O3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="P3" s="7"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
     </row>
@@ -1242,7 +1240,7 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
@@ -1286,47 +1284,47 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1364,19 +1362,15 @@
         <v>70</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P6" s="1">
-        <f t="shared" ref="P6:P10" si="0">H6*900</f>
-        <v>180000000</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D23" si="1">E6+1</f>
+        <f t="shared" ref="D7:D25" si="0">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -1410,18 +1404,15 @@
         <v>80</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2001</v>
       </c>
       <c r="E8" s="1">
@@ -1455,19 +1446,15 @@
         <v>90</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P8" s="1">
-        <f t="shared" si="0"/>
-        <v>360000000</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3001</v>
       </c>
       <c r="E9" s="1">
@@ -1501,18 +1488,15 @@
         <v>100</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4001</v>
       </c>
       <c r="E10" s="1">
@@ -1546,19 +1530,15 @@
         <v>1</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P10" s="1">
-        <f t="shared" si="0"/>
-        <v>540000000</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5001</v>
       </c>
       <c r="E11" s="1">
@@ -1592,18 +1572,15 @@
         <v>1</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6001</v>
       </c>
       <c r="E12" s="1">
@@ -1637,19 +1614,15 @@
         <v>1</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P12" s="1">
-        <f>H12*900</f>
-        <v>720000000</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7001</v>
       </c>
       <c r="E13" s="1">
@@ -1683,18 +1656,15 @@
         <v>1</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8001</v>
       </c>
       <c r="E14" s="1">
@@ -1728,19 +1698,15 @@
         <v>1</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P14" s="1">
-        <f>H14*900</f>
-        <v>900000000</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9001</v>
       </c>
       <c r="E15" s="1">
@@ -1774,10 +1740,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P15" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1785,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10001</v>
       </c>
       <c r="E16" s="1">
@@ -1819,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1827,7 +1790,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>15001</v>
       </c>
       <c r="E17" s="1">
@@ -1861,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1869,7 +1832,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>20001</v>
       </c>
       <c r="E18" s="1">
@@ -1903,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1911,7 +1874,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>21001</v>
       </c>
       <c r="E19" s="1">
@@ -1945,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1953,7 +1916,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>25001</v>
       </c>
       <c r="E20" s="1">
@@ -1987,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1995,7 +1958,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>26001</v>
       </c>
       <c r="E21" s="1">
@@ -2029,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2037,7 +2000,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>30001</v>
       </c>
       <c r="E22" s="1">
@@ -2071,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2079,7 +2042,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>31001</v>
       </c>
       <c r="E23" s="1">
@@ -2113,18 +2076,92 @@
         <v>1</v>
       </c>
       <c r="O23" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="0"/>
+        <v>35001</v>
+      </c>
+      <c r="E24" s="1">
+        <v>36000</v>
+      </c>
+      <c r="F24" s="5">
+        <v>9</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4003</v>
+      </c>
+      <c r="H24" s="1">
+        <v>10</v>
+      </c>
+      <c r="I24" s="8">
+        <v>15</v>
+      </c>
+      <c r="J24" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K24" s="8">
+        <v>90</v>
+      </c>
+      <c r="L24" s="1">
+        <v>4</v>
+      </c>
+      <c r="M24" s="1">
+        <v>36</v>
+      </c>
+      <c r="N24" s="1">
+        <v>1</v>
+      </c>
+      <c r="O24" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="0"/>
+        <v>36001</v>
+      </c>
+      <c r="E25" s="1">
+        <v>40000</v>
+      </c>
+      <c r="F25" s="5">
+        <v>9</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4003</v>
+      </c>
+      <c r="H25" s="1">
+        <v>10</v>
+      </c>
+      <c r="I25" s="8">
+        <v>15</v>
+      </c>
+      <c r="J25" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K25" s="8">
+        <v>90</v>
+      </c>
+      <c r="L25" s="1">
+        <v>4</v>
+      </c>
+      <c r="M25" s="1">
+        <v>22</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="9:11">
       <c r="I27" s="8"/>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -2112,7 +2112,7 @@
         <v>4</v>
       </c>
       <c r="M24" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N24" s="1">
         <v>1</v>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -340,12 +340,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1141,22 +1141,22 @@
   <dimension ref="A1:R45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="14.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="3" customWidth="1"/>
-    <col min="10" max="11" width="14.5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.125" style="2" customWidth="1"/>
-    <col min="13" max="14" width="14.5" style="2" customWidth="1"/>
-    <col min="15" max="15" width="34.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.25" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="9.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.1238938053097" style="1" customWidth="1"/>
+    <col min="6" max="7" width="14.1238938053097" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.5044247787611" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.1238938053097" style="3" customWidth="1"/>
+    <col min="10" max="11" width="14.5044247787611" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.1238938053097" style="2" customWidth="1"/>
+    <col min="13" max="14" width="14.5044247787611" style="2" customWidth="1"/>
+    <col min="15" max="15" width="34.6283185840708" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.2477876106195" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8.12389380530973" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.6283185840708" style="2" customWidth="1"/>
     <col min="19" max="19" width="9" style="2"/>
-    <col min="20" max="20" width="8.5" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.50442477876106" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1370,7 +1370,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D25" si="0">E6+1</f>
+        <f t="shared" ref="D7:D26" si="0">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -2161,6 +2161,48 @@
       </c>
       <c r="O25" s="1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" si="0"/>
+        <v>40001</v>
+      </c>
+      <c r="E26" s="1">
+        <v>45000</v>
+      </c>
+      <c r="F26" s="5">
+        <v>9</v>
+      </c>
+      <c r="G26" s="1">
+        <v>4004</v>
+      </c>
+      <c r="H26" s="1">
+        <v>2</v>
+      </c>
+      <c r="I26" s="8">
+        <v>15</v>
+      </c>
+      <c r="J26" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K26" s="8">
+        <v>90</v>
+      </c>
+      <c r="L26" s="1">
+        <v>4</v>
+      </c>
+      <c r="M26" s="1">
+        <v>28</v>
+      </c>
+      <c r="N26" s="1">
+        <v>1</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="9:11">

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowWidth="18355" windowHeight="6840"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -340,12 +340,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1141,22 +1141,22 @@
   <dimension ref="A1:R45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.87826086956522" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.1238938053097" style="1" customWidth="1"/>
-    <col min="6" max="7" width="14.1238938053097" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.5044247787611" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.1238938053097" style="3" customWidth="1"/>
-    <col min="10" max="11" width="14.5044247787611" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.1238938053097" style="2" customWidth="1"/>
-    <col min="13" max="14" width="14.5044247787611" style="2" customWidth="1"/>
-    <col min="15" max="15" width="34.6283185840708" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.2477876106195" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.12389380530973" style="2" customWidth="1"/>
-    <col min="18" max="18" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.87826086956522" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.1217391304348" style="1" customWidth="1"/>
+    <col min="6" max="7" width="14.1217391304348" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.504347826087" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.1217391304348" style="3" customWidth="1"/>
+    <col min="10" max="11" width="14.504347826087" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.1217391304348" style="2" customWidth="1"/>
+    <col min="13" max="14" width="14.504347826087" style="2" customWidth="1"/>
+    <col min="15" max="15" width="34.6260869565217" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.2434782608696" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8.12173913043478" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.62608695652174" style="2" customWidth="1"/>
     <col min="19" max="19" width="9" style="2"/>
-    <col min="20" max="20" width="8.50442477876106" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.50434782608696" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2175,7 +2175,7 @@
         <v>45000</v>
       </c>
       <c r="F26" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G26" s="1">
         <v>4004</v>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18355" windowHeight="6840"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -144,7 +144,22 @@
     <t>传世劵，等级丹，特戒自选</t>
   </si>
   <si>
-    <t>副本劵，等级丹，神器</t>
+    <t>副本劵，等级丹，青龙神器</t>
+  </si>
+  <si>
+    <t>副本劵，等级丹， 特戒</t>
+  </si>
+  <si>
+    <t>BOSS卷，等级丹，魂骨自选</t>
+  </si>
+  <si>
+    <t>副本劵，等级丹，白虎神器</t>
+  </si>
+  <si>
+    <t>副本劵，等级丹，11技能自选</t>
+  </si>
+  <si>
+    <t>副本劵，等级丹，朱雀神器</t>
   </si>
 </sst>
 </file>
@@ -1141,22 +1156,22 @@
   <dimension ref="A1:R45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87826086956522" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.87826086956522" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.1217391304348" style="1" customWidth="1"/>
-    <col min="6" max="7" width="14.1217391304348" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.504347826087" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.1217391304348" style="3" customWidth="1"/>
-    <col min="10" max="11" width="14.504347826087" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.1217391304348" style="2" customWidth="1"/>
-    <col min="13" max="14" width="14.504347826087" style="2" customWidth="1"/>
-    <col min="15" max="15" width="34.6260869565217" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.2434782608696" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.12173913043478" style="2" customWidth="1"/>
-    <col min="18" max="18" width="9.62608695652174" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="14.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.5083333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.125" style="3" customWidth="1"/>
+    <col min="10" max="11" width="14.5083333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.125" style="2" customWidth="1"/>
+    <col min="13" max="14" width="14.5083333333333" style="2" customWidth="1"/>
+    <col min="15" max="15" width="34.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.2416666666667" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8.125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.625" style="2" customWidth="1"/>
     <col min="19" max="19" width="9" style="2"/>
-    <col min="20" max="20" width="8.50434782608696" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.50833333333333" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1370,7 +1385,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D26" si="0">E6+1</f>
+        <f t="shared" ref="D7:D29" si="0">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -2160,7 +2175,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2202,23 +2217,134 @@
         <v>1</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="9:11">
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="0"/>
+        <v>45001</v>
+      </c>
+      <c r="E27" s="1">
+        <v>46000</v>
+      </c>
+      <c r="F27" s="5">
+        <v>9</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4003</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="8">
+        <v>15</v>
+      </c>
+      <c r="J27" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K27" s="8">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>4</v>
+      </c>
+      <c r="M27" s="1">
+        <v>37</v>
+      </c>
+      <c r="N27" s="1">
+        <v>1</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="0"/>
+        <v>46001</v>
+      </c>
+      <c r="E28" s="1">
+        <v>49000</v>
+      </c>
+      <c r="F28" s="5">
+        <v>9</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4003</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="8">
+        <v>15</v>
+      </c>
+      <c r="J28" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K28" s="8">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>4</v>
+      </c>
+      <c r="M28" s="1">
+        <v>29</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="0"/>
+        <v>49001</v>
+      </c>
+      <c r="E29" s="1">
+        <v>50000</v>
+      </c>
+      <c r="F29" s="5">
+        <v>9</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4003</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="8">
+        <v>15</v>
+      </c>
+      <c r="J29" s="8">
+        <v>4014</v>
+      </c>
+      <c r="K29" s="8">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>4</v>
+      </c>
+      <c r="M29" s="1">
+        <v>38</v>
+      </c>
+      <c r="N29" s="1">
+        <v>1</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="30" customHeight="1" spans="8:14">
       <c r="H30" s="1"/>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>副本劵，等级丹，朱雀神器</t>
+  </si>
+  <si>
+    <t>boss劵，等级丹，魂骨</t>
+  </si>
+  <si>
+    <t>boss劵，等级丹，金宠精华</t>
   </si>
 </sst>
 </file>
@@ -366,12 +372,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -696,7 +708,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -720,16 +732,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -738,102 +750,106 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1156,188 +1172,188 @@
   <dimension ref="A1:R45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2"/>
+    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="14.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.5083333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="3" customWidth="1"/>
-    <col min="10" max="11" width="14.5083333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.125" style="2" customWidth="1"/>
-    <col min="13" max="14" width="14.5083333333333" style="2" customWidth="1"/>
+    <col min="6" max="7" width="14.125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.5083333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="14.125" style="4" customWidth="1"/>
+    <col min="10" max="11" width="14.5083333333333" style="4" customWidth="1"/>
+    <col min="12" max="12" width="14.125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="14.5083333333333" style="3" customWidth="1"/>
     <col min="15" max="15" width="34.625" style="1" customWidth="1"/>
     <col min="16" max="16" width="11.2416666666667" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="9.625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9" style="2"/>
-    <col min="20" max="20" width="8.50833333333333" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="17" max="17" width="8.125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9" style="3"/>
+    <col min="20" max="20" width="8.50833333333333" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="1">
@@ -1352,19 +1368,19 @@
       <c r="F6" s="1">
         <v>5</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="6">
         <v>4002</v>
       </c>
       <c r="H6" s="1">
         <v>200000</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="11">
         <v>9</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="11">
         <v>4003</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="11">
         <v>70</v>
       </c>
       <c r="L6" s="1">
@@ -1385,7 +1401,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D29" si="0">E6+1</f>
+        <f t="shared" ref="D7:D32" si="0">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -1394,19 +1410,19 @@
       <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <v>4001</v>
       </c>
       <c r="H7" s="1">
         <v>20000</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="11">
         <v>9</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="11">
         <v>4003</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="11">
         <v>80</v>
       </c>
       <c r="L7" s="1">
@@ -1436,19 +1452,19 @@
       <c r="F8" s="1">
         <v>5</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="6">
         <v>4002</v>
       </c>
       <c r="H8" s="1">
         <v>400000</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="11">
         <v>9</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="11">
         <v>4003</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="11">
         <v>90</v>
       </c>
       <c r="L8" s="1">
@@ -1484,13 +1500,13 @@
       <c r="H9" s="1">
         <v>40000</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="11">
         <v>9</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="11">
         <v>4003</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="11">
         <v>100</v>
       </c>
       <c r="L9" s="1">
@@ -1520,19 +1536,19 @@
       <c r="F10" s="1">
         <v>5</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="6">
         <v>4002</v>
       </c>
       <c r="H10" s="1">
         <v>600000</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="11">
         <v>15</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="11">
         <v>4014</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="11">
         <v>10</v>
       </c>
       <c r="L10" s="1">
@@ -1568,13 +1584,13 @@
       <c r="H11" s="1">
         <v>60000</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="11">
         <v>15</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="11">
         <v>4014</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="11">
         <v>20</v>
       </c>
       <c r="L11" s="1">
@@ -1604,19 +1620,19 @@
       <c r="F12" s="1">
         <v>5</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="6">
         <v>4002</v>
       </c>
       <c r="H12" s="1">
         <v>800000</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="11">
         <v>15</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="11">
         <v>4014</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="11">
         <v>30</v>
       </c>
       <c r="L12" s="1">
@@ -1652,13 +1668,13 @@
       <c r="H13" s="1">
         <v>80000</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="11">
         <v>15</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="11">
         <v>4014</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="11">
         <v>40</v>
       </c>
       <c r="L13" s="1">
@@ -1694,13 +1710,13 @@
       <c r="H14" s="1">
         <v>1000000</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="11">
         <v>15</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="11">
         <v>4014</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="11">
         <v>50</v>
       </c>
       <c r="L14" s="1">
@@ -1736,13 +1752,13 @@
       <c r="H15" s="1">
         <v>100000</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="11">
         <v>15</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="11">
         <v>4014</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="11">
         <v>60</v>
       </c>
       <c r="L15" s="1">
@@ -1778,13 +1794,13 @@
       <c r="H16" s="1">
         <v>5</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="11">
         <v>15</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="11">
         <v>4014</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="11">
         <v>70</v>
       </c>
       <c r="L16" s="1">
@@ -1820,13 +1836,13 @@
       <c r="H17" s="1">
         <v>1</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="11">
         <v>15</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="11">
         <v>4014</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="11">
         <v>70</v>
       </c>
       <c r="L17" s="1">
@@ -1862,13 +1878,13 @@
       <c r="H18" s="1">
         <v>10</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="11">
         <v>15</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="11">
         <v>4014</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="11">
         <v>80</v>
       </c>
       <c r="L18" s="1">
@@ -1904,13 +1920,13 @@
       <c r="H19" s="1">
         <v>10</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="11">
         <v>15</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="11">
         <v>4014</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="11">
         <v>80</v>
       </c>
       <c r="L19" s="1">
@@ -1937,7 +1953,7 @@
       <c r="E20" s="1">
         <v>26000</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="6">
         <v>5</v>
       </c>
       <c r="G20" s="1">
@@ -1946,13 +1962,13 @@
       <c r="H20" s="1">
         <v>2</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="11">
         <v>15</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="11">
         <v>4014</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="11">
         <v>90</v>
       </c>
       <c r="L20" s="1">
@@ -1979,7 +1995,7 @@
       <c r="E21" s="1">
         <v>30000</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="6">
         <v>5</v>
       </c>
       <c r="G21" s="1">
@@ -1988,13 +2004,13 @@
       <c r="H21" s="1">
         <v>2</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="11">
         <v>15</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="11">
         <v>4014</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="11">
         <v>90</v>
       </c>
       <c r="L21" s="1">
@@ -2021,7 +2037,7 @@
       <c r="E22" s="1">
         <v>31000</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="6">
         <v>9</v>
       </c>
       <c r="G22" s="1">
@@ -2030,13 +2046,13 @@
       <c r="H22" s="1">
         <v>1</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="11">
         <v>15</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="11">
         <v>4014</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="11">
         <v>90</v>
       </c>
       <c r="L22" s="1">
@@ -2063,7 +2079,7 @@
       <c r="E23" s="1">
         <v>35000</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="6">
         <v>9</v>
       </c>
       <c r="G23" s="1">
@@ -2072,13 +2088,13 @@
       <c r="H23" s="1">
         <v>1</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="11">
         <v>15</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="11">
         <v>4014</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="11">
         <v>90</v>
       </c>
       <c r="L23" s="1">
@@ -2105,7 +2121,7 @@
       <c r="E24" s="1">
         <v>36000</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="6">
         <v>9</v>
       </c>
       <c r="G24" s="1">
@@ -2114,13 +2130,13 @@
       <c r="H24" s="1">
         <v>10</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="11">
         <v>15</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="11">
         <v>4014</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="11">
         <v>90</v>
       </c>
       <c r="L24" s="1">
@@ -2147,7 +2163,7 @@
       <c r="E25" s="1">
         <v>40000</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="6">
         <v>9</v>
       </c>
       <c r="G25" s="1">
@@ -2156,13 +2172,13 @@
       <c r="H25" s="1">
         <v>10</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="11">
         <v>15</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="11">
         <v>4014</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="11">
         <v>90</v>
       </c>
       <c r="L25" s="1">
@@ -2189,7 +2205,7 @@
       <c r="E26" s="1">
         <v>45000</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="6">
         <v>5</v>
       </c>
       <c r="G26" s="1">
@@ -2198,13 +2214,13 @@
       <c r="H26" s="1">
         <v>2</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="11">
         <v>15</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="11">
         <v>4014</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="11">
         <v>90</v>
       </c>
       <c r="L26" s="1">
@@ -2231,7 +2247,7 @@
       <c r="E27" s="1">
         <v>46000</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="6">
         <v>9</v>
       </c>
       <c r="G27" s="1">
@@ -2240,13 +2256,13 @@
       <c r="H27" s="1">
         <v>20</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="11">
         <v>15</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="11">
         <v>4014</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="11">
         <v>100</v>
       </c>
       <c r="L27" s="1">
@@ -2273,7 +2289,7 @@
       <c r="E28" s="1">
         <v>49000</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="6">
         <v>9</v>
       </c>
       <c r="G28" s="1">
@@ -2282,13 +2298,13 @@
       <c r="H28" s="1">
         <v>20</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="11">
         <v>15</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="11">
         <v>4014</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="11">
         <v>100</v>
       </c>
       <c r="L28" s="1">
@@ -2315,7 +2331,7 @@
       <c r="E29" s="1">
         <v>50000</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="6">
         <v>9</v>
       </c>
       <c r="G29" s="1">
@@ -2324,13 +2340,13 @@
       <c r="H29" s="1">
         <v>20</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="11">
         <v>15</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="11">
         <v>4014</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="11">
         <v>100</v>
       </c>
       <c r="L29" s="1">
@@ -2346,115 +2362,202 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="8:14">
-      <c r="H30" s="1"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="8:14">
-      <c r="H31" s="1"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="8:14">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C30" s="7">
+        <v>25</v>
+      </c>
+      <c r="D30" s="7">
+        <f t="shared" si="0"/>
+        <v>50001</v>
+      </c>
+      <c r="E30" s="7">
+        <v>53000</v>
+      </c>
+      <c r="F30" s="8">
+        <v>9</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4004</v>
+      </c>
+      <c r="H30" s="7">
+        <v>2</v>
+      </c>
+      <c r="I30" s="12">
+        <v>15</v>
+      </c>
+      <c r="J30" s="12">
+        <v>4014</v>
+      </c>
+      <c r="K30" s="12">
+        <v>100</v>
+      </c>
+      <c r="L30" s="7">
+        <v>4</v>
+      </c>
+      <c r="M30" s="7">
+        <v>28</v>
+      </c>
+      <c r="N30" s="7">
+        <v>1</v>
+      </c>
+      <c r="O30" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P30" s="7"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:15">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" si="0"/>
+        <v>53001</v>
+      </c>
+      <c r="E31" s="1">
+        <v>55000</v>
+      </c>
+      <c r="F31" s="6">
+        <v>9</v>
+      </c>
+      <c r="G31" s="1">
+        <v>4004</v>
+      </c>
+      <c r="H31" s="1">
+        <v>2</v>
+      </c>
+      <c r="I31" s="11">
+        <v>15</v>
+      </c>
+      <c r="J31" s="11">
+        <v>4014</v>
+      </c>
+      <c r="K31" s="11">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>5</v>
+      </c>
+      <c r="M31" s="1">
+        <v>4025</v>
+      </c>
+      <c r="N31" s="1">
+        <v>1</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="6:14">
+      <c r="F32" s="6"/>
+      <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
     </row>
-    <row r="33" customHeight="1" spans="8:14">
+    <row r="33" customHeight="1" spans="6:14">
+      <c r="F33" s="6"/>
+      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" customHeight="1" spans="8:14">
+    <row r="34" customHeight="1" spans="6:14">
+      <c r="F34" s="6"/>
+      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
     </row>
-    <row r="35" customHeight="1" spans="8:14">
+    <row r="35" customHeight="1" spans="6:14">
+      <c r="F35" s="6"/>
+      <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
     </row>
     <row r="36" customHeight="1" spans="8:14">
       <c r="H36" s="1"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
     <row r="37" customHeight="1" spans="8:14">
       <c r="H37" s="1"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
     <row r="38" customHeight="1" spans="8:14">
       <c r="H38" s="1"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
     </row>
     <row r="39" customHeight="1" spans="8:14">
       <c r="H39" s="1"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
     </row>
     <row r="40" customHeight="1" spans="8:14">
       <c r="H40" s="1"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
     </row>
     <row r="41" customHeight="1" spans="8:14">
       <c r="H41" s="1"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
     </row>
     <row r="42" customHeight="1" spans="8:14">
       <c r="H42" s="1"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="8:14">
       <c r="H43" s="1"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
     </row>
     <row r="44" customHeight="1" spans="8:14">
       <c r="H44" s="1"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
     </row>
     <row r="45" customHeight="1" spans="8:14">
       <c r="H45" s="1"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
     </row>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -165,7 +165,7 @@
     <t>boss劵，等级丹，魂骨</t>
   </si>
   <si>
-    <t>boss劵，等级丹，金宠精华</t>
+    <t>boss劵，等级丹，时装精华</t>
   </si>
 </sst>
 </file>
@@ -2438,7 +2438,7 @@
         <v>5</v>
       </c>
       <c r="M31" s="1">
-        <v>4025</v>
+        <v>4034</v>
       </c>
       <c r="N31" s="1">
         <v>1</v>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -162,10 +162,10 @@
     <t>副本劵，等级丹，朱雀神器</t>
   </si>
   <si>
-    <t>boss劵，等级丹，魂骨</t>
-  </si>
-  <si>
     <t>boss劵，等级丹，时装精华</t>
+  </si>
+  <si>
+    <t>boss劵，等级丹，金色魂心</t>
   </si>
 </sst>
 </file>
@@ -2391,11 +2391,11 @@
       <c r="K30" s="12">
         <v>100</v>
       </c>
-      <c r="L30" s="7">
-        <v>4</v>
+      <c r="L30" s="1">
+        <v>5</v>
       </c>
       <c r="M30" s="7">
-        <v>28</v>
+        <v>4034</v>
       </c>
       <c r="N30" s="7">
         <v>1</v>
@@ -2438,7 +2438,7 @@
         <v>5</v>
       </c>
       <c r="M31" s="1">
-        <v>4034</v>
+        <v>4025</v>
       </c>
       <c r="N31" s="1">
         <v>1</v>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -204,15 +204,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFC00000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -841,14 +841,14 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1242,13 +1242,13 @@
       <c r="H3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="L3" s="5" t="s">
@@ -1260,10 +1260,10 @@
       <c r="N3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="10"/>
+      <c r="P3" s="7"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
@@ -1288,13 +1288,13 @@
       <c r="H4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="6" t="s">
         <v>8</v>
       </c>
       <c r="L4" s="5" t="s">
@@ -1306,8 +1306,8 @@
       <c r="N4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
     </row>
@@ -1332,13 +1332,13 @@
       <c r="H5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="6" t="s">
         <v>14</v>
       </c>
       <c r="L5" s="5" t="s">
@@ -1350,12 +1350,12 @@
       <c r="N5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1368,19 +1368,19 @@
       <c r="F6" s="1">
         <v>5</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="8">
         <v>4002</v>
       </c>
       <c r="H6" s="1">
         <v>200000</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="9">
         <v>9</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="9">
         <v>4003</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="9">
         <v>70</v>
       </c>
       <c r="L6" s="1">
@@ -1396,7 +1396,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1410,19 +1410,19 @@
       <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="8">
         <v>4001</v>
       </c>
       <c r="H7" s="1">
         <v>20000</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="9">
         <v>9</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="9">
         <v>4003</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="9">
         <v>80</v>
       </c>
       <c r="L7" s="1">
@@ -1438,7 +1438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1452,19 +1452,19 @@
       <c r="F8" s="1">
         <v>5</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="8">
         <v>4002</v>
       </c>
       <c r="H8" s="1">
         <v>400000</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <v>9</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="9">
         <v>4003</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="9">
         <v>90</v>
       </c>
       <c r="L8" s="1">
@@ -1480,7 +1480,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1500,13 +1500,13 @@
       <c r="H9" s="1">
         <v>40000</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="9">
         <v>9</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="9">
         <v>4003</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="9">
         <v>100</v>
       </c>
       <c r="L9" s="1">
@@ -1522,7 +1522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1536,19 +1536,19 @@
       <c r="F10" s="1">
         <v>5</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="8">
         <v>4002</v>
       </c>
       <c r="H10" s="1">
         <v>600000</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="9">
         <v>15</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="9">
         <v>4014</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="9">
         <v>10</v>
       </c>
       <c r="L10" s="1">
@@ -1564,7 +1564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1584,13 +1584,13 @@
       <c r="H11" s="1">
         <v>60000</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="9">
         <v>15</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="9">
         <v>4014</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="9">
         <v>20</v>
       </c>
       <c r="L11" s="1">
@@ -1606,7 +1606,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1620,19 +1620,19 @@
       <c r="F12" s="1">
         <v>5</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="8">
         <v>4002</v>
       </c>
       <c r="H12" s="1">
         <v>800000</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="9">
         <v>15</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="9">
         <v>4014</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="9">
         <v>30</v>
       </c>
       <c r="L12" s="1">
@@ -1648,7 +1648,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1668,13 +1668,13 @@
       <c r="H13" s="1">
         <v>80000</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="9">
         <v>15</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="9">
         <v>4014</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="9">
         <v>40</v>
       </c>
       <c r="L13" s="1">
@@ -1690,7 +1690,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1710,13 +1710,13 @@
       <c r="H14" s="1">
         <v>1000000</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="9">
         <v>15</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="9">
         <v>4014</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="9">
         <v>50</v>
       </c>
       <c r="L14" s="1">
@@ -1732,7 +1732,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1752,13 +1752,13 @@
       <c r="H15" s="1">
         <v>100000</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="9">
         <v>15</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="9">
         <v>4014</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="9">
         <v>60</v>
       </c>
       <c r="L15" s="1">
@@ -1774,7 +1774,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1794,13 +1794,13 @@
       <c r="H16" s="1">
         <v>5</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="9">
         <v>15</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="9">
         <v>4014</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="9">
         <v>70</v>
       </c>
       <c r="L16" s="1">
@@ -1816,7 +1816,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1836,13 +1836,13 @@
       <c r="H17" s="1">
         <v>1</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="9">
         <v>15</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="9">
         <v>4014</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="9">
         <v>70</v>
       </c>
       <c r="L17" s="1">
@@ -1858,7 +1858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1878,13 +1878,13 @@
       <c r="H18" s="1">
         <v>10</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="9">
         <v>15</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="9">
         <v>4014</v>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="9">
         <v>80</v>
       </c>
       <c r="L18" s="1">
@@ -1900,7 +1900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1920,13 +1920,13 @@
       <c r="H19" s="1">
         <v>10</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="9">
         <v>15</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="9">
         <v>4014</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="9">
         <v>80</v>
       </c>
       <c r="L19" s="1">
@@ -1942,7 +1942,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1953,7 +1953,7 @@
       <c r="E20" s="1">
         <v>26000</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="8">
         <v>5</v>
       </c>
       <c r="G20" s="1">
@@ -1962,13 +1962,13 @@
       <c r="H20" s="1">
         <v>2</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="9">
         <v>15</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="9">
         <v>4014</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="9">
         <v>90</v>
       </c>
       <c r="L20" s="1">
@@ -1984,7 +1984,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1995,7 +1995,7 @@
       <c r="E21" s="1">
         <v>30000</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="8">
         <v>5</v>
       </c>
       <c r="G21" s="1">
@@ -2004,13 +2004,13 @@
       <c r="H21" s="1">
         <v>2</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="9">
         <v>15</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="9">
         <v>4014</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="9">
         <v>90</v>
       </c>
       <c r="L21" s="1">
@@ -2026,7 +2026,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -2037,7 +2037,7 @@
       <c r="E22" s="1">
         <v>31000</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="8">
         <v>9</v>
       </c>
       <c r="G22" s="1">
@@ -2046,13 +2046,13 @@
       <c r="H22" s="1">
         <v>1</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="9">
         <v>15</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="9">
         <v>4014</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="9">
         <v>90</v>
       </c>
       <c r="L22" s="1">
@@ -2068,7 +2068,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -2079,7 +2079,7 @@
       <c r="E23" s="1">
         <v>35000</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="8">
         <v>9</v>
       </c>
       <c r="G23" s="1">
@@ -2088,13 +2088,13 @@
       <c r="H23" s="1">
         <v>1</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="9">
         <v>15</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="9">
         <v>4014</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="9">
         <v>90</v>
       </c>
       <c r="L23" s="1">
@@ -2110,7 +2110,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -2121,7 +2121,7 @@
       <c r="E24" s="1">
         <v>36000</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="8">
         <v>9</v>
       </c>
       <c r="G24" s="1">
@@ -2130,13 +2130,13 @@
       <c r="H24" s="1">
         <v>10</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="9">
         <v>15</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="9">
         <v>4014</v>
       </c>
-      <c r="K24" s="11">
+      <c r="K24" s="9">
         <v>90</v>
       </c>
       <c r="L24" s="1">
@@ -2152,7 +2152,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -2163,7 +2163,7 @@
       <c r="E25" s="1">
         <v>40000</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="8">
         <v>9</v>
       </c>
       <c r="G25" s="1">
@@ -2172,13 +2172,13 @@
       <c r="H25" s="1">
         <v>10</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="9">
         <v>15</v>
       </c>
-      <c r="J25" s="11">
+      <c r="J25" s="9">
         <v>4014</v>
       </c>
-      <c r="K25" s="11">
+      <c r="K25" s="9">
         <v>90</v>
       </c>
       <c r="L25" s="1">
@@ -2194,7 +2194,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -2205,7 +2205,7 @@
       <c r="E26" s="1">
         <v>45000</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="8">
         <v>5</v>
       </c>
       <c r="G26" s="1">
@@ -2214,13 +2214,13 @@
       <c r="H26" s="1">
         <v>2</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="9">
         <v>15</v>
       </c>
-      <c r="J26" s="11">
+      <c r="J26" s="9">
         <v>4014</v>
       </c>
-      <c r="K26" s="11">
+      <c r="K26" s="9">
         <v>90</v>
       </c>
       <c r="L26" s="1">
@@ -2236,7 +2236,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -2247,7 +2247,7 @@
       <c r="E27" s="1">
         <v>46000</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="8">
         <v>9</v>
       </c>
       <c r="G27" s="1">
@@ -2256,13 +2256,13 @@
       <c r="H27" s="1">
         <v>20</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="9">
         <v>15</v>
       </c>
-      <c r="J27" s="11">
+      <c r="J27" s="9">
         <v>4014</v>
       </c>
-      <c r="K27" s="11">
+      <c r="K27" s="9">
         <v>100</v>
       </c>
       <c r="L27" s="1">
@@ -2278,7 +2278,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="E28" s="1">
         <v>49000</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="8">
         <v>9</v>
       </c>
       <c r="G28" s="1">
@@ -2298,13 +2298,13 @@
       <c r="H28" s="1">
         <v>20</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="9">
         <v>15</v>
       </c>
-      <c r="J28" s="11">
+      <c r="J28" s="9">
         <v>4014</v>
       </c>
-      <c r="K28" s="11">
+      <c r="K28" s="9">
         <v>100</v>
       </c>
       <c r="L28" s="1">
@@ -2320,7 +2320,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -2331,7 +2331,7 @@
       <c r="E29" s="1">
         <v>50000</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="8">
         <v>9</v>
       </c>
       <c r="G29" s="1">
@@ -2340,13 +2340,13 @@
       <c r="H29" s="1">
         <v>20</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="9">
         <v>15</v>
       </c>
-      <c r="J29" s="11">
+      <c r="J29" s="9">
         <v>4014</v>
       </c>
-      <c r="K29" s="11">
+      <c r="K29" s="9">
         <v>100</v>
       </c>
       <c r="L29" s="1">
@@ -2363,23 +2363,23 @@
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C30" s="7">
+      <c r="C30" s="10">
         <v>25</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="10">
         <f t="shared" si="0"/>
         <v>50001</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="10">
         <v>53000</v>
       </c>
-      <c r="F30" s="8">
-        <v>9</v>
+      <c r="F30" s="11">
+        <v>5</v>
       </c>
       <c r="G30" s="1">
         <v>4004</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="10">
         <v>2</v>
       </c>
       <c r="I30" s="12">
@@ -2394,18 +2394,18 @@
       <c r="L30" s="1">
         <v>5</v>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="10">
         <v>4034</v>
       </c>
-      <c r="N30" s="7">
-        <v>1</v>
-      </c>
-      <c r="O30" s="7" t="s">
+      <c r="N30" s="10">
+        <v>1</v>
+      </c>
+      <c r="O30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P30" s="7"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:15">
+      <c r="P30" s="10"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:16">
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -2416,8 +2416,8 @@
       <c r="E31" s="1">
         <v>55000</v>
       </c>
-      <c r="F31" s="6">
-        <v>9</v>
+      <c r="F31" s="11">
+        <v>5</v>
       </c>
       <c r="G31" s="1">
         <v>4004</v>
@@ -2425,13 +2425,13 @@
       <c r="H31" s="1">
         <v>2</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="9">
         <v>15</v>
       </c>
-      <c r="J31" s="11">
+      <c r="J31" s="9">
         <v>4014</v>
       </c>
-      <c r="K31" s="11">
+      <c r="K31" s="9">
         <v>100</v>
       </c>
       <c r="L31" s="1">
@@ -2447,117 +2447,117 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="6:14">
-      <c r="F32" s="6"/>
+    <row r="32" customHeight="1" spans="3:16">
+      <c r="F32" s="8"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
     </row>
     <row r="33" customHeight="1" spans="6:14">
-      <c r="F33" s="6"/>
+      <c r="F33" s="8"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
     <row r="34" customHeight="1" spans="6:14">
-      <c r="F34" s="6"/>
+      <c r="F34" s="8"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
     </row>
     <row r="35" customHeight="1" spans="6:14">
-      <c r="F35" s="6"/>
+      <c r="F35" s="8"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
     </row>
-    <row r="36" customHeight="1" spans="8:14">
+    <row r="36" customHeight="1" spans="6:14">
       <c r="H36" s="1"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" customHeight="1" spans="8:14">
+    <row r="37" customHeight="1" spans="6:14">
       <c r="H37" s="1"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
-    <row r="38" customHeight="1" spans="8:14">
+    <row r="38" customHeight="1" spans="6:14">
       <c r="H38" s="1"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" customHeight="1" spans="8:14">
+    <row r="39" customHeight="1" spans="6:14">
       <c r="H39" s="1"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
     </row>
-    <row r="40" customHeight="1" spans="8:14">
+    <row r="40" customHeight="1" spans="6:14">
       <c r="H40" s="1"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="8:14">
+    <row r="41" customHeight="1" spans="6:14">
       <c r="H41" s="1"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
     </row>
-    <row r="42" customHeight="1" spans="8:14">
+    <row r="42" customHeight="1" spans="6:14">
       <c r="H42" s="1"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" customHeight="1" spans="8:14">
+    <row r="43" customHeight="1" spans="6:14">
       <c r="H43" s="1"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
     </row>
-    <row r="44" customHeight="1" spans="8:14">
+    <row r="44" customHeight="1" spans="6:14">
       <c r="H44" s="1"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
     </row>
-    <row r="45" customHeight="1" spans="8:14">
+    <row r="45" customHeight="1" spans="6:14">
       <c r="H45" s="1"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
     </row>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t>ID</t>
   </si>
@@ -166,6 +166,15 @@
   </si>
   <si>
     <t>boss劵，等级丹，金色魂心</t>
+  </si>
+  <si>
+    <t>副本劵，等级丹，玄武神器</t>
+  </si>
+  <si>
+    <t>副本劵，等级丹，魂骨自选</t>
+  </si>
+  <si>
+    <t>副本劵，等级丹，麒麟神器</t>
   </si>
 </sst>
 </file>
@@ -832,9 +841,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -847,6 +857,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1172,188 +1184,188 @@
   <dimension ref="A1:R45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3"/>
+    <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9" style="4"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="14.125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.5083333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="4" customWidth="1"/>
-    <col min="10" max="11" width="14.5083333333333" style="4" customWidth="1"/>
-    <col min="12" max="12" width="14.125" style="3" customWidth="1"/>
-    <col min="13" max="14" width="14.5083333333333" style="3" customWidth="1"/>
+    <col min="6" max="7" width="14.125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.5083333333333" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.125" style="5" customWidth="1"/>
+    <col min="10" max="11" width="14.5083333333333" style="5" customWidth="1"/>
+    <col min="12" max="12" width="14.125" style="4" customWidth="1"/>
+    <col min="13" max="14" width="14.5083333333333" style="4" customWidth="1"/>
     <col min="15" max="15" width="34.625" style="1" customWidth="1"/>
     <col min="16" max="16" width="11.2416666666667" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.625" style="3" customWidth="1"/>
-    <col min="19" max="19" width="9" style="3"/>
-    <col min="20" max="20" width="8.50833333333333" style="3" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="3"/>
+    <col min="17" max="17" width="8.125" style="4" customWidth="1"/>
+    <col min="18" max="18" width="9.625" style="4" customWidth="1"/>
+    <col min="19" max="19" width="9" style="4"/>
+    <col min="20" max="20" width="8.50833333333333" style="4" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C6" s="1">
@@ -1368,19 +1380,19 @@
       <c r="F6" s="1">
         <v>5</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="9">
         <v>4002</v>
       </c>
       <c r="H6" s="1">
         <v>200000</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="10">
         <v>9</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="10">
         <v>4003</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="10">
         <v>70</v>
       </c>
       <c r="L6" s="1">
@@ -1401,7 +1413,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D32" si="0">E6+1</f>
+        <f t="shared" ref="D7:D34" si="0">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -1410,19 +1422,19 @@
       <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="9">
         <v>4001</v>
       </c>
       <c r="H7" s="1">
         <v>20000</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="10">
         <v>9</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="10">
         <v>4003</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="10">
         <v>80</v>
       </c>
       <c r="L7" s="1">
@@ -1452,19 +1464,19 @@
       <c r="F8" s="1">
         <v>5</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="9">
         <v>4002</v>
       </c>
       <c r="H8" s="1">
         <v>400000</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="10">
         <v>9</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="10">
         <v>4003</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="10">
         <v>90</v>
       </c>
       <c r="L8" s="1">
@@ -1500,13 +1512,13 @@
       <c r="H9" s="1">
         <v>40000</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="10">
         <v>9</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="10">
         <v>4003</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="10">
         <v>100</v>
       </c>
       <c r="L9" s="1">
@@ -1536,19 +1548,19 @@
       <c r="F10" s="1">
         <v>5</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="9">
         <v>4002</v>
       </c>
       <c r="H10" s="1">
         <v>600000</v>
       </c>
-      <c r="I10" s="9">
-        <v>15</v>
-      </c>
-      <c r="J10" s="9">
+      <c r="I10" s="10">
+        <v>15</v>
+      </c>
+      <c r="J10" s="10">
         <v>4014</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="10">
         <v>10</v>
       </c>
       <c r="L10" s="1">
@@ -1584,13 +1596,13 @@
       <c r="H11" s="1">
         <v>60000</v>
       </c>
-      <c r="I11" s="9">
-        <v>15</v>
-      </c>
-      <c r="J11" s="9">
+      <c r="I11" s="10">
+        <v>15</v>
+      </c>
+      <c r="J11" s="10">
         <v>4014</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="10">
         <v>20</v>
       </c>
       <c r="L11" s="1">
@@ -1620,19 +1632,19 @@
       <c r="F12" s="1">
         <v>5</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="9">
         <v>4002</v>
       </c>
       <c r="H12" s="1">
         <v>800000</v>
       </c>
-      <c r="I12" s="9">
-        <v>15</v>
-      </c>
-      <c r="J12" s="9">
+      <c r="I12" s="10">
+        <v>15</v>
+      </c>
+      <c r="J12" s="10">
         <v>4014</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="10">
         <v>30</v>
       </c>
       <c r="L12" s="1">
@@ -1668,13 +1680,13 @@
       <c r="H13" s="1">
         <v>80000</v>
       </c>
-      <c r="I13" s="9">
-        <v>15</v>
-      </c>
-      <c r="J13" s="9">
+      <c r="I13" s="10">
+        <v>15</v>
+      </c>
+      <c r="J13" s="10">
         <v>4014</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="10">
         <v>40</v>
       </c>
       <c r="L13" s="1">
@@ -1710,13 +1722,13 @@
       <c r="H14" s="1">
         <v>1000000</v>
       </c>
-      <c r="I14" s="9">
-        <v>15</v>
-      </c>
-      <c r="J14" s="9">
+      <c r="I14" s="10">
+        <v>15</v>
+      </c>
+      <c r="J14" s="10">
         <v>4014</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="10">
         <v>50</v>
       </c>
       <c r="L14" s="1">
@@ -1752,13 +1764,13 @@
       <c r="H15" s="1">
         <v>100000</v>
       </c>
-      <c r="I15" s="9">
-        <v>15</v>
-      </c>
-      <c r="J15" s="9">
+      <c r="I15" s="10">
+        <v>15</v>
+      </c>
+      <c r="J15" s="10">
         <v>4014</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="10">
         <v>60</v>
       </c>
       <c r="L15" s="1">
@@ -1794,13 +1806,13 @@
       <c r="H16" s="1">
         <v>5</v>
       </c>
-      <c r="I16" s="9">
-        <v>15</v>
-      </c>
-      <c r="J16" s="9">
+      <c r="I16" s="10">
+        <v>15</v>
+      </c>
+      <c r="J16" s="10">
         <v>4014</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="10">
         <v>70</v>
       </c>
       <c r="L16" s="1">
@@ -1836,13 +1848,13 @@
       <c r="H17" s="1">
         <v>1</v>
       </c>
-      <c r="I17" s="9">
-        <v>15</v>
-      </c>
-      <c r="J17" s="9">
+      <c r="I17" s="10">
+        <v>15</v>
+      </c>
+      <c r="J17" s="10">
         <v>4014</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="10">
         <v>70</v>
       </c>
       <c r="L17" s="1">
@@ -1878,13 +1890,13 @@
       <c r="H18" s="1">
         <v>10</v>
       </c>
-      <c r="I18" s="9">
-        <v>15</v>
-      </c>
-      <c r="J18" s="9">
+      <c r="I18" s="10">
+        <v>15</v>
+      </c>
+      <c r="J18" s="10">
         <v>4014</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="10">
         <v>80</v>
       </c>
       <c r="L18" s="1">
@@ -1920,13 +1932,13 @@
       <c r="H19" s="1">
         <v>10</v>
       </c>
-      <c r="I19" s="9">
-        <v>15</v>
-      </c>
-      <c r="J19" s="9">
+      <c r="I19" s="10">
+        <v>15</v>
+      </c>
+      <c r="J19" s="10">
         <v>4014</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="10">
         <v>80</v>
       </c>
       <c r="L19" s="1">
@@ -1953,7 +1965,7 @@
       <c r="E20" s="1">
         <v>26000</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="9">
         <v>5</v>
       </c>
       <c r="G20" s="1">
@@ -1962,13 +1974,13 @@
       <c r="H20" s="1">
         <v>2</v>
       </c>
-      <c r="I20" s="9">
-        <v>15</v>
-      </c>
-      <c r="J20" s="9">
+      <c r="I20" s="10">
+        <v>15</v>
+      </c>
+      <c r="J20" s="10">
         <v>4014</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="10">
         <v>90</v>
       </c>
       <c r="L20" s="1">
@@ -1995,7 +2007,7 @@
       <c r="E21" s="1">
         <v>30000</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="9">
         <v>5</v>
       </c>
       <c r="G21" s="1">
@@ -2004,13 +2016,13 @@
       <c r="H21" s="1">
         <v>2</v>
       </c>
-      <c r="I21" s="9">
-        <v>15</v>
-      </c>
-      <c r="J21" s="9">
+      <c r="I21" s="10">
+        <v>15</v>
+      </c>
+      <c r="J21" s="10">
         <v>4014</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="10">
         <v>90</v>
       </c>
       <c r="L21" s="1">
@@ -2037,7 +2049,7 @@
       <c r="E22" s="1">
         <v>31000</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="9">
         <v>9</v>
       </c>
       <c r="G22" s="1">
@@ -2046,13 +2058,13 @@
       <c r="H22" s="1">
         <v>1</v>
       </c>
-      <c r="I22" s="9">
-        <v>15</v>
-      </c>
-      <c r="J22" s="9">
+      <c r="I22" s="10">
+        <v>15</v>
+      </c>
+      <c r="J22" s="10">
         <v>4014</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="10">
         <v>90</v>
       </c>
       <c r="L22" s="1">
@@ -2079,7 +2091,7 @@
       <c r="E23" s="1">
         <v>35000</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <v>9</v>
       </c>
       <c r="G23" s="1">
@@ -2088,13 +2100,13 @@
       <c r="H23" s="1">
         <v>1</v>
       </c>
-      <c r="I23" s="9">
-        <v>15</v>
-      </c>
-      <c r="J23" s="9">
+      <c r="I23" s="10">
+        <v>15</v>
+      </c>
+      <c r="J23" s="10">
         <v>4014</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="10">
         <v>90</v>
       </c>
       <c r="L23" s="1">
@@ -2121,7 +2133,7 @@
       <c r="E24" s="1">
         <v>36000</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="9">
         <v>9</v>
       </c>
       <c r="G24" s="1">
@@ -2130,13 +2142,13 @@
       <c r="H24" s="1">
         <v>10</v>
       </c>
-      <c r="I24" s="9">
-        <v>15</v>
-      </c>
-      <c r="J24" s="9">
+      <c r="I24" s="10">
+        <v>15</v>
+      </c>
+      <c r="J24" s="10">
         <v>4014</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="10">
         <v>90</v>
       </c>
       <c r="L24" s="1">
@@ -2163,7 +2175,7 @@
       <c r="E25" s="1">
         <v>40000</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="9">
         <v>9</v>
       </c>
       <c r="G25" s="1">
@@ -2172,13 +2184,13 @@
       <c r="H25" s="1">
         <v>10</v>
       </c>
-      <c r="I25" s="9">
-        <v>15</v>
-      </c>
-      <c r="J25" s="9">
+      <c r="I25" s="10">
+        <v>15</v>
+      </c>
+      <c r="J25" s="10">
         <v>4014</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="10">
         <v>90</v>
       </c>
       <c r="L25" s="1">
@@ -2205,7 +2217,7 @@
       <c r="E26" s="1">
         <v>45000</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="9">
         <v>5</v>
       </c>
       <c r="G26" s="1">
@@ -2214,13 +2226,13 @@
       <c r="H26" s="1">
         <v>2</v>
       </c>
-      <c r="I26" s="9">
-        <v>15</v>
-      </c>
-      <c r="J26" s="9">
+      <c r="I26" s="10">
+        <v>15</v>
+      </c>
+      <c r="J26" s="10">
         <v>4014</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="10">
         <v>90</v>
       </c>
       <c r="L26" s="1">
@@ -2247,7 +2259,7 @@
       <c r="E27" s="1">
         <v>46000</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="9">
         <v>9</v>
       </c>
       <c r="G27" s="1">
@@ -2256,13 +2268,13 @@
       <c r="H27" s="1">
         <v>20</v>
       </c>
-      <c r="I27" s="9">
-        <v>15</v>
-      </c>
-      <c r="J27" s="9">
+      <c r="I27" s="10">
+        <v>15</v>
+      </c>
+      <c r="J27" s="10">
         <v>4014</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="10">
         <v>100</v>
       </c>
       <c r="L27" s="1">
@@ -2289,7 +2301,7 @@
       <c r="E28" s="1">
         <v>49000</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="9">
         <v>9</v>
       </c>
       <c r="G28" s="1">
@@ -2298,13 +2310,13 @@
       <c r="H28" s="1">
         <v>20</v>
       </c>
-      <c r="I28" s="9">
-        <v>15</v>
-      </c>
-      <c r="J28" s="9">
+      <c r="I28" s="10">
+        <v>15</v>
+      </c>
+      <c r="J28" s="10">
         <v>4014</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="10">
         <v>100</v>
       </c>
       <c r="L28" s="1">
@@ -2331,7 +2343,7 @@
       <c r="E29" s="1">
         <v>50000</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="9">
         <v>9</v>
       </c>
       <c r="G29" s="1">
@@ -2340,13 +2352,13 @@
       <c r="H29" s="1">
         <v>20</v>
       </c>
-      <c r="I29" s="9">
-        <v>15</v>
-      </c>
-      <c r="J29" s="9">
+      <c r="I29" s="10">
+        <v>15</v>
+      </c>
+      <c r="J29" s="10">
         <v>4014</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="10">
         <v>100</v>
       </c>
       <c r="L29" s="1">
@@ -2363,201 +2375,300 @@
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C30" s="10">
+      <c r="C30" s="11">
         <v>25</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="11">
         <f t="shared" si="0"/>
         <v>50001</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="11">
         <v>53000</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="12">
         <v>5</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="11">
         <v>4004</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="11">
         <v>2</v>
       </c>
-      <c r="I30" s="12">
-        <v>15</v>
-      </c>
-      <c r="J30" s="12">
+      <c r="I30" s="10">
+        <v>15</v>
+      </c>
+      <c r="J30" s="10">
         <v>4014</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="10">
         <v>100</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30" s="11">
         <v>5</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="11">
         <v>4034</v>
       </c>
-      <c r="N30" s="10">
-        <v>1</v>
-      </c>
-      <c r="O30" s="10" t="s">
+      <c r="N30" s="11">
+        <v>1</v>
+      </c>
+      <c r="O30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="P30" s="10"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:16">
-      <c r="C31" s="1">
+      <c r="P30" s="11"/>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C31" s="11">
         <v>26</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="11">
         <f t="shared" si="0"/>
         <v>53001</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="11">
         <v>55000</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="12">
         <v>5</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" s="11">
         <v>4004</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="11">
         <v>2</v>
       </c>
-      <c r="I31" s="9">
-        <v>15</v>
-      </c>
-      <c r="J31" s="9">
+      <c r="I31" s="10">
+        <v>15</v>
+      </c>
+      <c r="J31" s="10">
         <v>4014</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="10">
         <v>100</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L31" s="11">
         <v>5</v>
       </c>
-      <c r="M31" s="1">
+      <c r="M31" s="11">
         <v>4025</v>
       </c>
-      <c r="N31" s="1">
-        <v>1</v>
-      </c>
-      <c r="O31" s="1" t="s">
+      <c r="N31" s="11">
+        <v>1</v>
+      </c>
+      <c r="O31" s="11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:16">
-      <c r="F32" s="8"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="6:14">
-      <c r="F33" s="8"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="6:14">
-      <c r="F34" s="8"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="6:14">
-      <c r="F35" s="8"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="6:14">
+      <c r="P31" s="11"/>
+    </row>
+    <row r="32" s="3" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C32" s="11">
+        <v>27</v>
+      </c>
+      <c r="D32" s="13">
+        <f t="shared" si="0"/>
+        <v>55001</v>
+      </c>
+      <c r="E32" s="13">
+        <v>56000</v>
+      </c>
+      <c r="F32" s="14">
+        <v>9</v>
+      </c>
+      <c r="G32" s="1">
+        <v>4003</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="15">
+        <v>15</v>
+      </c>
+      <c r="J32" s="15">
+        <v>4014</v>
+      </c>
+      <c r="K32" s="15">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>4</v>
+      </c>
+      <c r="M32" s="1">
+        <v>39</v>
+      </c>
+      <c r="N32" s="13">
+        <v>1</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P32" s="13"/>
+    </row>
+    <row r="33" customHeight="1" spans="3:15">
+      <c r="C33" s="11">
+        <v>28</v>
+      </c>
+      <c r="D33" s="11">
+        <f t="shared" si="0"/>
+        <v>56001</v>
+      </c>
+      <c r="E33" s="11">
+        <v>59000</v>
+      </c>
+      <c r="F33" s="12">
+        <v>9</v>
+      </c>
+      <c r="G33" s="11">
+        <v>4003</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="10">
+        <v>15</v>
+      </c>
+      <c r="J33" s="10">
+        <v>4014</v>
+      </c>
+      <c r="K33" s="10">
+        <v>100</v>
+      </c>
+      <c r="L33" s="1">
+        <v>4</v>
+      </c>
+      <c r="M33" s="1">
+        <v>28</v>
+      </c>
+      <c r="N33" s="11">
+        <v>1</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:15">
+      <c r="C34" s="11">
+        <v>29</v>
+      </c>
+      <c r="D34" s="11">
+        <f t="shared" si="0"/>
+        <v>59001</v>
+      </c>
+      <c r="E34" s="11">
+        <v>60000</v>
+      </c>
+      <c r="F34" s="12">
+        <v>9</v>
+      </c>
+      <c r="G34" s="11">
+        <v>4003</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="10">
+        <v>15</v>
+      </c>
+      <c r="J34" s="10">
+        <v>4014</v>
+      </c>
+      <c r="K34" s="10">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1">
+        <v>4</v>
+      </c>
+      <c r="M34" s="1">
+        <v>40</v>
+      </c>
+      <c r="N34" s="11">
+        <v>1</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:15">
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+    </row>
+    <row r="36" customHeight="1" spans="3:15">
       <c r="H36" s="1"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" customHeight="1" spans="6:14">
+    <row r="37" customHeight="1" spans="3:15">
       <c r="H37" s="1"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
-    <row r="38" customHeight="1" spans="6:14">
+    <row r="38" customHeight="1" spans="3:15">
       <c r="H38" s="1"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" customHeight="1" spans="6:14">
+    <row r="39" customHeight="1" spans="3:15">
       <c r="H39" s="1"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
     </row>
-    <row r="40" customHeight="1" spans="6:14">
+    <row r="40" customHeight="1" spans="3:15">
       <c r="H40" s="1"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="6:14">
+    <row r="41" customHeight="1" spans="3:15">
       <c r="H41" s="1"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
     </row>
-    <row r="42" customHeight="1" spans="6:14">
+    <row r="42" customHeight="1" spans="3:15">
       <c r="H42" s="1"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" customHeight="1" spans="6:14">
+    <row r="43" customHeight="1" spans="3:15">
       <c r="H43" s="1"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
     </row>
-    <row r="44" customHeight="1" spans="6:14">
+    <row r="44" customHeight="1" spans="3:15">
       <c r="H44" s="1"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
     </row>
-    <row r="45" customHeight="1" spans="6:14">
+    <row r="45" customHeight="1" spans="3:15">
       <c r="H45" s="1"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
     </row>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -175,6 +175,12 @@
   </si>
   <si>
     <t>副本劵，等级丹，麒麟神器</t>
+  </si>
+  <si>
+    <t>BOSS劵，等级丹，金色魂心</t>
+  </si>
+  <si>
+    <t>副本劵，等级丹，暗金魂心</t>
   </si>
 </sst>
 </file>
@@ -370,12 +376,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1413,7 +1419,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D34" si="0">E6+1</f>
+        <f t="shared" ref="D7:D36" si="0">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -2588,26 +2594,88 @@
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:15">
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
+      <c r="C35" s="11">
+        <v>30</v>
+      </c>
+      <c r="D35" s="11">
+        <f t="shared" si="0"/>
+        <v>60001</v>
+      </c>
+      <c r="E35" s="11">
+        <v>64000</v>
+      </c>
+      <c r="F35" s="12">
+        <v>5</v>
+      </c>
+      <c r="G35" s="11">
+        <v>4004</v>
+      </c>
+      <c r="H35" s="1">
+        <v>3</v>
+      </c>
+      <c r="I35" s="10">
+        <v>15</v>
+      </c>
+      <c r="J35" s="10">
+        <v>4014</v>
+      </c>
+      <c r="K35" s="10">
+        <v>100</v>
+      </c>
+      <c r="L35" s="11">
+        <v>5</v>
+      </c>
+      <c r="M35" s="11">
+        <v>4025</v>
+      </c>
+      <c r="N35" s="11">
+        <v>1</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="36" customHeight="1" spans="3:15">
-      <c r="H36" s="1"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
+      <c r="C36" s="11">
+        <v>31</v>
+      </c>
+      <c r="D36" s="11">
+        <f t="shared" si="0"/>
+        <v>64001</v>
+      </c>
+      <c r="E36" s="11">
+        <v>65000</v>
+      </c>
+      <c r="F36" s="12">
+        <v>5</v>
+      </c>
+      <c r="G36" s="11">
+        <v>4004</v>
+      </c>
+      <c r="H36" s="1">
+        <v>3</v>
+      </c>
+      <c r="I36" s="10">
+        <v>15</v>
+      </c>
+      <c r="J36" s="10">
+        <v>4014</v>
+      </c>
+      <c r="K36" s="10">
+        <v>100</v>
+      </c>
+      <c r="L36" s="11">
+        <v>5</v>
+      </c>
+      <c r="M36" s="11">
+        <v>4041</v>
+      </c>
+      <c r="N36" s="11">
+        <v>1</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="37" customHeight="1" spans="3:15">
       <c r="H37" s="1"/>

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -61,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -181,6 +186,12 @@
   </si>
   <si>
     <t>副本劵，等级丹，暗金魂心</t>
+  </si>
+  <si>
+    <t>BOSS劵，等级丹，时装精华</t>
+  </si>
+  <si>
+    <t>BOSS劵，等级丹，极戒</t>
   </si>
 </sst>
 </file>
@@ -376,12 +387,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1187,7 +1198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
@@ -1419,7 +1430,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D36" si="0">E6+1</f>
+        <f t="shared" ref="D7:D39" si="0">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -2678,18 +2689,88 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:15">
-      <c r="H37" s="1"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
+      <c r="C37" s="11">
+        <v>32</v>
+      </c>
+      <c r="D37" s="11">
+        <f t="shared" si="0"/>
+        <v>65001</v>
+      </c>
+      <c r="E37" s="11">
+        <v>69000</v>
+      </c>
+      <c r="F37" s="12">
+        <v>5</v>
+      </c>
+      <c r="G37" s="11">
+        <v>4004</v>
+      </c>
+      <c r="H37" s="1">
+        <v>3</v>
+      </c>
+      <c r="I37" s="10">
+        <v>15</v>
+      </c>
+      <c r="J37" s="10">
+        <v>4014</v>
+      </c>
+      <c r="K37" s="10">
+        <v>100</v>
+      </c>
+      <c r="L37" s="11">
+        <v>5</v>
+      </c>
+      <c r="M37" s="11">
+        <v>4034</v>
+      </c>
+      <c r="N37" s="11">
+        <v>1</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="38" customHeight="1" spans="3:15">
-      <c r="H38" s="1"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
+      <c r="C38" s="11">
+        <v>34</v>
+      </c>
+      <c r="D38" s="11">
+        <f t="shared" si="0"/>
+        <v>69001</v>
+      </c>
+      <c r="E38" s="11">
+        <v>70000</v>
+      </c>
+      <c r="F38" s="12">
+        <v>5</v>
+      </c>
+      <c r="G38" s="11">
+        <v>4004</v>
+      </c>
+      <c r="H38" s="1">
+        <v>3</v>
+      </c>
+      <c r="I38" s="10">
+        <v>15</v>
+      </c>
+      <c r="J38" s="10">
+        <v>4014</v>
+      </c>
+      <c r="K38" s="10">
+        <v>100</v>
+      </c>
+      <c r="L38" s="11">
+        <v>4</v>
+      </c>
+      <c r="M38" s="11">
+        <v>44</v>
+      </c>
+      <c r="N38" s="11">
+        <v>1</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="39" customHeight="1" spans="3:15">
       <c r="H39" s="1"/>
@@ -2732,13 +2813,6 @@
       <c r="K44" s="10"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="3:15">
-      <c r="H45" s="1"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -1430,7 +1430,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D39" si="0">E6+1</f>
+        <f t="shared" ref="D7:D41" si="0">E6+1</f>
         <v>1001</v>
       </c>
       <c r="E7" s="1">
@@ -2773,25 +2773,130 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:15">
-      <c r="H39" s="1"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
+      <c r="C39" s="11">
+        <v>35</v>
+      </c>
+      <c r="D39" s="11">
+        <f t="shared" si="0"/>
+        <v>70001</v>
+      </c>
+      <c r="E39" s="11">
+        <v>73000</v>
+      </c>
+      <c r="F39" s="12">
+        <v>5</v>
+      </c>
+      <c r="G39" s="11">
+        <v>4004</v>
+      </c>
+      <c r="H39" s="1">
+        <v>3</v>
+      </c>
+      <c r="I39" s="10">
+        <v>15</v>
+      </c>
+      <c r="J39" s="10">
+        <v>4014</v>
+      </c>
+      <c r="K39" s="10">
+        <v>100</v>
+      </c>
+      <c r="L39" s="11">
+        <v>5</v>
+      </c>
+      <c r="M39" s="11">
+        <v>4034</v>
+      </c>
+      <c r="N39" s="11">
+        <v>1</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="40" customHeight="1" spans="3:15">
-      <c r="H40" s="1"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
+      <c r="C40" s="11">
+        <v>36</v>
+      </c>
+      <c r="D40" s="11">
+        <f t="shared" si="0"/>
+        <v>73001</v>
+      </c>
+      <c r="E40" s="11">
+        <v>74000</v>
+      </c>
+      <c r="F40" s="12">
+        <v>5</v>
+      </c>
+      <c r="G40" s="11">
+        <v>4004</v>
+      </c>
+      <c r="H40" s="1">
+        <v>3</v>
+      </c>
+      <c r="I40" s="10">
+        <v>15</v>
+      </c>
+      <c r="J40" s="10">
+        <v>4014</v>
+      </c>
+      <c r="K40" s="10">
+        <v>100</v>
+      </c>
+      <c r="L40" s="11">
+        <v>5</v>
+      </c>
+      <c r="M40" s="11">
+        <v>4025</v>
+      </c>
+      <c r="N40" s="11">
+        <v>1</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="41" customHeight="1" spans="3:15">
-      <c r="H41" s="1"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
+      <c r="C41" s="11">
+        <v>37</v>
+      </c>
+      <c r="D41" s="11">
+        <f t="shared" si="0"/>
+        <v>74001</v>
+      </c>
+      <c r="E41" s="11">
+        <v>75000</v>
+      </c>
+      <c r="F41" s="12">
+        <v>5</v>
+      </c>
+      <c r="G41" s="11">
+        <v>4004</v>
+      </c>
+      <c r="H41" s="1">
+        <v>3</v>
+      </c>
+      <c r="I41" s="10">
+        <v>15</v>
+      </c>
+      <c r="J41" s="10">
+        <v>4014</v>
+      </c>
+      <c r="K41" s="10">
+        <v>100</v>
+      </c>
+      <c r="L41" s="11">
+        <v>4</v>
+      </c>
+      <c r="M41" s="11">
+        <v>44</v>
+      </c>
+      <c r="N41" s="11">
+        <v>1</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="42" customHeight="1" spans="3:15">
       <c r="H42" s="1"/>
